--- a/docs/Journal-de-Travail_BorminKiril.xlsx
+++ b/docs/Journal-de-Travail_BorminKiril.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\px20umf\Documents\GitHub\secured_webshop\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D373F5A2-FE58-4BE3-AE8C-36A8F7C9319B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18EF340-211B-40C2-825A-FE9AD8AB2093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5625" yWindow="2670" windowWidth="21600" windowHeight="11385" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="54">
   <si>
     <t>Journal de travail</t>
   </si>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t>Améliorer l'affichage des erreurs (trop de tentatives d'entrer le mdp, etc)</t>
+  </si>
+  <si>
+    <t>Refaire john the ripper</t>
   </si>
 </sst>
 </file>
@@ -1240,7 +1243,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>530</c:v>
+                  <c:v>560</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -2753,7 +2756,7 @@
       <c r="B3" s="85"/>
       <c r="C3" s="11" t="str">
         <f>QUOTIENT(E4,60)&amp;" heures "&amp;MOD(E4,60)&amp;" minutes"</f>
-        <v>8 heures 50 minutes</v>
+        <v>9 heures 20 minutes</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="13"/>
@@ -2772,11 +2775,11 @@
       </c>
       <c r="D4" s="12">
         <f>SUBTOTAL(9,$D$7:$D$531)</f>
-        <v>410</v>
+        <v>440</v>
       </c>
       <c r="E4" s="16">
         <f>SUM(C4:D4)</f>
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="F4" s="14"/>
       <c r="G4" s="17"/>
@@ -3218,15 +3221,23 @@
       <c r="G22" s="36"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="str">
+      <c r="A23" s="31">
         <f>IF(ISBLANK(B23),"",_xlfn.ISOWEEKNUM('Journal de travail'!$B23))</f>
-        <v/>
-      </c>
-      <c r="B23" s="37"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="37">
+        <v>46171</v>
+      </c>
       <c r="C23" s="38"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="29"/>
+      <c r="D23" s="39">
+        <v>30</v>
+      </c>
+      <c r="E23" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>53</v>
+      </c>
       <c r="G23" s="41"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -9514,11 +9525,11 @@
       </c>
       <c r="B7">
         <f>SUMIF('Journal de travail'!$E$7:$E$532,Plannification!E7,'Journal de travail'!$D$7:$D$532)</f>
-        <v>410</v>
+        <v>440</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="E7" s="64" t="str">
         <f>'Journal de travail'!M9</f>
@@ -9526,7 +9537,7 @@
       </c>
       <c r="F7" s="65" t="str">
         <f t="shared" si="1"/>
-        <v>8 h 50 min</v>
+        <v>9 h 20 min</v>
       </c>
       <c r="G7" s="66">
         <f>SUM(A7:B7)/$C$11</f>
@@ -9660,22 +9671,22 @@
       </c>
       <c r="B11">
         <f>SUM(B6:B10)</f>
-        <v>410</v>
+        <v>440</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
-        <v>530</v>
+        <v>560</v>
       </c>
       <c r="E11" s="78" t="s">
         <v>43</v>
       </c>
       <c r="F11" s="59" t="str">
         <f t="shared" si="1"/>
-        <v>8 h 50 min</v>
+        <v>9 h 20 min</v>
       </c>
       <c r="G11" s="79">
         <f>C11/C12</f>
-        <v>9.8148148148148151E-2</v>
+        <v>0.1037037037037037</v>
       </c>
       <c r="L11" s="80" t="s">
         <v>43</v>
